--- a/outputs/All_States_historical_prices.xlsx
+++ b/outputs/All_States_historical_prices.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSW" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QLD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIC" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SA" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="NSW" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="QLD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="VIC" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SA" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="TAS" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6043,16 +6043,16 @@
         </is>
       </c>
       <c r="B274" s="3" t="n">
-        <v>71.2</v>
+        <v>70.36</v>
       </c>
       <c r="C274" s="3" t="n">
-        <v>74.36</v>
+        <v>71.44</v>
       </c>
       <c r="D274" s="3" t="n">
-        <v>71.2</v>
+        <v>70.36</v>
       </c>
       <c r="E274" s="3" t="n">
-        <v>74.36</v>
+        <v>71.44</v>
       </c>
       <c r="F274" s="4" t="inlineStr"/>
     </row>
@@ -11673,16 +11673,16 @@
         </is>
       </c>
       <c r="B274" s="3" t="n">
-        <v>65.23</v>
+        <v>62.64</v>
       </c>
       <c r="C274" s="3" t="n">
-        <v>65.02</v>
+        <v>61.19</v>
       </c>
       <c r="D274" s="3" t="n">
-        <v>65.23</v>
+        <v>62.64</v>
       </c>
       <c r="E274" s="3" t="n">
-        <v>65.02</v>
+        <v>61.19</v>
       </c>
       <c r="F274" s="4" t="inlineStr"/>
     </row>
@@ -17303,16 +17303,16 @@
         </is>
       </c>
       <c r="B274" s="3" t="n">
-        <v>41.17</v>
+        <v>44.74</v>
       </c>
       <c r="C274" s="3" t="n">
-        <v>44.39</v>
+        <v>44.69</v>
       </c>
       <c r="D274" s="3" t="n">
-        <v>41.17</v>
+        <v>44.74</v>
       </c>
       <c r="E274" s="3" t="n">
-        <v>44.39</v>
+        <v>44.69</v>
       </c>
       <c r="F274" s="4" t="inlineStr"/>
     </row>
@@ -22933,16 +22933,16 @@
         </is>
       </c>
       <c r="B274" s="3" t="n">
-        <v>43.95</v>
+        <v>52.8</v>
       </c>
       <c r="C274" s="3" t="n">
-        <v>35.84</v>
+        <v>40.82</v>
       </c>
       <c r="D274" s="3" t="n">
-        <v>43.95</v>
+        <v>52.8</v>
       </c>
       <c r="E274" s="3" t="n">
-        <v>35.84</v>
+        <v>40.82</v>
       </c>
       <c r="F274" s="4" t="inlineStr"/>
     </row>
@@ -28123,16 +28123,16 @@
         </is>
       </c>
       <c r="B252" s="3" t="n">
-        <v>88.23999999999999</v>
+        <v>91.04000000000001</v>
       </c>
       <c r="C252" s="3" t="n">
-        <v>88.52</v>
+        <v>90.94</v>
       </c>
       <c r="D252" s="3" t="n">
-        <v>88.23999999999999</v>
+        <v>91.04000000000001</v>
       </c>
       <c r="E252" s="3" t="n">
-        <v>88.52</v>
+        <v>90.94</v>
       </c>
       <c r="F252" s="4" t="inlineStr"/>
     </row>
